--- a/ktb_arb/국채선물_차익거래.xlsx
+++ b/ktb_arb/국채선물_차익거래.xlsx
@@ -625,6 +625,7 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -910,6 +911,7 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -937,6 +939,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -951,9 +954,10 @@
       <c r="C5" s="7" t="n">
         <v>117.52</v>
       </c>
-      <c r="D5" s="8">
-        <f>IMFX("F 10YKTB","현재가")</f>
-        <v/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>=IMFX("F 10YKTB","현재가")</t>
+        </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
@@ -975,9 +979,10 @@
       <c r="C6" s="7" t="n">
         <v>117.51</v>
       </c>
-      <c r="D6" s="8">
-        <f>IMFX("F 10YKTB","매수1호가")</f>
-        <v/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>=IMFX("F 10YKTB","매수1호가")</t>
+        </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -999,9 +1004,10 @@
       <c r="C7" s="7" t="n">
         <v>117.53</v>
       </c>
-      <c r="D7" s="8">
-        <f>IMFX("F 10YKTB","매도1호가")</f>
-        <v/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>=IMFX("F 10YKTB","매도1호가")</t>
+        </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
@@ -1020,9 +1026,10 @@
         <f>AVERAGE(C6:C7)</f>
         <v/>
       </c>
-      <c r="D8" s="8">
-        <f>AVERAGE(C6:C7)</f>
-        <v/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>=AVERAGE(C6:C7)</t>
+        </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
@@ -1030,6 +1037,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -1044,9 +1052,10 @@
       <c r="C10" s="7" t="n">
         <v>2.96</v>
       </c>
-      <c r="D10" s="8">
-        <f>IMFX("KR103502GE97","매수수익률")</f>
-        <v/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>=IMFX("KR103502GE97","매수수익률")</t>
+        </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
@@ -1068,9 +1077,10 @@
       <c r="C11" s="7" t="n">
         <v>2.95</v>
       </c>
-      <c r="D11" s="8">
-        <f>IMFX("KR103502GE97","매도수익률")</f>
-        <v/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>=IMFX("KR103502GE97","매도수익률")</t>
+        </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
@@ -1092,9 +1102,10 @@
       <c r="C12" s="7" t="n">
         <v>2.97</v>
       </c>
-      <c r="D12" s="8">
-        <f>IMFX("KR103503GF95","매수수익률")</f>
-        <v/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>=IMFX("KR103503GF95","매수수익률")</t>
+        </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
@@ -1116,9 +1127,10 @@
       <c r="C13" s="7" t="n">
         <v>2.96</v>
       </c>
-      <c r="D13" s="8">
-        <f>IMFX("KR103503GF95","매도수익률")</f>
-        <v/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>=IMFX("KR103503GF95","매도수익률")</t>
+        </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -1140,9 +1152,10 @@
       <c r="C14" s="7" t="n">
         <v>2.98</v>
       </c>
-      <c r="D14" s="8">
-        <f>IMFX("KR103504GH93","매수수익률")</f>
-        <v/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>=IMFX("KR103504GH93","매수수익률")</t>
+        </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -1164,9 +1177,10 @@
       <c r="C15" s="7" t="n">
         <v>2.97</v>
       </c>
-      <c r="D15" s="8">
-        <f>IMFX("KR103504GH93","매도수익률")</f>
-        <v/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>=IMFX("KR103504GH93","매도수익률")</t>
+        </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
@@ -1174,6 +1188,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
@@ -1184,9 +1199,10 @@
       <c r="C17" s="7" t="n">
         <v>2.6</v>
       </c>
-      <c r="D17" s="8">
-        <f>IMFX("RP1D","금리")</f>
-        <v/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>=IMFX("RP1D","금리")</t>
+        </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
@@ -1204,9 +1220,10 @@
       <c r="C18" s="7" t="n">
         <v>2.75</v>
       </c>
-      <c r="D18" s="8">
-        <f>IMFX("CD91","금리")</f>
-        <v/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>=IMFX("CD91","금리")</t>
+        </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
@@ -1224,9 +1241,10 @@
       <c r="C19" s="7" t="n">
         <v>2.7</v>
       </c>
-      <c r="D19" s="8">
-        <f>IMFX("KTB3Y","수익률")</f>
-        <v/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>=IMFX("KTB3Y","수익률")</t>
+        </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
@@ -1234,6 +1252,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
@@ -1245,6 +1264,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
@@ -1294,6 +1314,7 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -1472,6 +1493,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -1579,6 +1601,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
@@ -1769,6 +1792,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
@@ -1906,6 +1930,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
@@ -2005,6 +2030,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
@@ -2072,6 +2098,7 @@
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2270,6 +2297,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
@@ -2404,6 +2432,7 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
@@ -2661,6 +2690,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
@@ -2757,9 +2787,10 @@
         <f>현금흐름!$AP$103</f>
         <v/>
       </c>
-      <c r="G36" s="8">
-        <f> 현물단가 + 조달이자 − 쿠폰FV</f>
-        <v/>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>현물단가 + 조달이자 − 쿠폰FV</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -2927,6 +2958,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
@@ -3182,6 +3214,7 @@
         <v/>
       </c>
     </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
@@ -3237,6 +3270,7 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -3325,6 +3359,7 @@
         <v/>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
@@ -3467,6 +3502,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
@@ -3594,6 +3630,7 @@
         <v/>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
@@ -3772,6 +3809,7 @@
         <v/>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
@@ -3820,6 +3858,7 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -3981,6 +4020,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
@@ -4095,6 +4135,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
@@ -4187,6 +4228,7 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="40" t="inlineStr">
         <is>
@@ -4295,6 +4337,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="40" t="inlineStr">
         <is>
@@ -4462,6 +4505,7 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
@@ -20513,6 +20557,7 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="11" t="inlineStr">
         <is>
@@ -20539,9 +20584,10 @@
           <t>연합인포맥스 (Excel Add-in)</t>
         </is>
       </c>
-      <c r="C5" s="53">
-        <f>IMFX("KR103502GE97","매도수익률")   /   =IMFX("F 10YKTB","현재가")</f>
-        <v/>
+      <c r="C5" s="53" t="inlineStr">
+        <is>
+          <t>=IMFX("KR103502GE97","매도수익률")   /   =IMFX("F 10YKTB","현재가")</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -20550,9 +20596,10 @@
           <t>Bloomberg (BDP)</t>
         </is>
       </c>
-      <c r="C6" s="53">
-        <f>BDP("KTBA Comdty","PX_LAST")   /   =BDP("KTB 3 06/10/35 Corp","YLD_YTM_ASK")</f>
-        <v/>
+      <c r="C6" s="53" t="inlineStr">
+        <is>
+          <t>=BDP("KTBA Comdty","PX_LAST")   /   =BDP("KTB 3 06/10/35 Corp","YLD_YTM_ASK")</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -20561,9 +20608,10 @@
           <t>Bloomberg (RTD 스트리밍)</t>
         </is>
       </c>
-      <c r="C7" s="53">
-        <f>RTD("bloomberglp.bloombergrtd",,"//blp/mktdata","KTBA Comdty","LAST_PRICE")</f>
-        <v/>
+      <c r="C7" s="53" t="inlineStr">
+        <is>
+          <t>=RTD("bloomberglp.bloombergrtd",,"//blp/mktdata","KTBA Comdty","LAST_PRICE")</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -20572,9 +20620,10 @@
           <t>Refinitiv Eikon</t>
         </is>
       </c>
-      <c r="C8" s="53">
-        <f>RtGet("IDN","KTBc1","CF_LAST")   또는  =TR("KTBc1","CF_LAST")</f>
-        <v/>
+      <c r="C8" s="53" t="inlineStr">
+        <is>
+          <t>=RtGet("IDN","KTBc1","CF_LAST")   또는  =TR("KTBc1","CF_LAST")</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -20583,9 +20632,10 @@
           <t>LS증권 xingAPI (DDE)</t>
         </is>
       </c>
-      <c r="C9" s="53">
-        <f>xingDDE|주식현재가!'종목코드'   (xingAPI DDE 서버 실행 필요)</f>
-        <v/>
+      <c r="C9" s="53" t="inlineStr">
+        <is>
+          <t>=xingDDE|주식현재가!'종목코드'   (xingAPI DDE 서버 실행 필요)</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -20594,9 +20644,10 @@
           <t>대신증권 CYBOS Plus (DDE)</t>
         </is>
       </c>
-      <c r="C10" s="53">
-        <f>CYBOS|StockMst!'A005930'   (CYBOS Plus 로그인 상태 필요)</f>
-        <v/>
+      <c r="C10" s="53" t="inlineStr">
+        <is>
+          <t>=CYBOS|StockMst!'A005930'   (CYBOS Plus 로그인 상태 필요)</t>
+        </is>
       </c>
     </row>
     <row r="11">
